--- a/Result/checkall/2026-09-20.xlsx
+++ b/Result/checkall/2026-09-20.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
